--- a/site/ADP-to-Microsoft-Dynamics-365-Finance-and-Operations-Integration/headings.xlsx
+++ b/site/ADP-to-Microsoft-Dynamics-365-Finance-and-Operations-Integration/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -639,7 +639,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Execution Features</t>
+          <t>Operational Settings</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -683,73 +683,73 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Manage System Users</t>
+          <t>Correlation Settings</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01KG2CNW00GSRPZC1M48NSHH0X</t>
+          <t>h_01KJCH2T30NXAWG485G8BNGJZQ</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-to-Microsoft-Dynamics-365-Finance-and-Operations-Integration/#h_01KG2CNW00GSRPZC1M48NSHH0X</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-to-Microsoft-Dynamics-365-Finance-and-Operations-Integration/#h_01KJCH2T30NXAWG485G8BNGJZQ</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Role Assignments</t>
+          <t>Source Filter Settings</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KG29Y4CNTPQWG91Z1EST2X0G</t>
+          <t>h_01KJCH4M0MPFPHM3SZMRJWWVTD</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-to-Microsoft-Dynamics-365-Finance-and-Operations-Integration/#h_01KG29Y4CNTPQWG91Z1EST2X0G</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-to-Microsoft-Dynamics-365-Finance-and-Operations-Integration/#h_01KJCH4M0MPFPHM3SZMRJWWVTD</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Provisioning Settings</t>
+          <t>Position Sync Settings</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KG29Y4CNKA3PNXHKG6F1C70Q</t>
+          <t>h_01KJCH1JHV0FAEAW2FXC2G73XW</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-to-Microsoft-Dynamics-365-Finance-and-Operations-Integration/#h_01KG29Y4CNKA3PNXHKG6F1C70Q</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-to-Microsoft-Dynamics-365-Finance-and-Operations-Integration/#h_01KJCH1JHV0FAEAW2FXC2G73XW</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Manage Warehouse Workers</t>
+          <t>Provisioning Settings</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -759,19 +759,19 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KG2CNW0097M9V6P3HN9EBTNZ</t>
+          <t>h_01KJCH1AJ4MSWYF57Y6X1EAXMB</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-to-Microsoft-Dynamics-365-Finance-and-Operations-Integration/#h_01KG2CNW0097M9V6P3HN9EBTNZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-to-Microsoft-Dynamics-365-Finance-and-Operations-Integration/#h_01KJCH1AJ4MSWYF57Y6X1EAXMB</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Manage Exflow Users</t>
+          <t>Provisioning Threshold</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -781,186 +781,670 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KG2C841Q142BEN21DPBX6P3V</t>
+          <t>h_01KJCH137APKATVJ1KB9HDWY32</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-to-Microsoft-Dynamics-365-Finance-and-Operations-Integration/#h_01KG2C841Q142BEN21DPBX6P3V</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-to-Microsoft-Dynamics-365-Finance-and-Operations-Integration/#h_01KJCH137APKATVJ1KB9HDWY32</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Notification Settings</t>
+          <t>Manage System Users</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KG2B3A4GH06FW1RKHC69T6G9</t>
+          <t>h_01KG2CNW00GSRPZC1M48NSHH0X</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-to-Microsoft-Dynamics-365-Finance-and-Operations-Integration/#h_01KG2B3A4GH06FW1RKHC69T6G9</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-to-Microsoft-Dynamics-365-Finance-and-Operations-Integration/#h_01KG2CNW00GSRPZC1M48NSHH0X</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Log Insights Settings</t>
+          <t>Correlation Settings</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KG2C1TN9NB041EAF6T6Y1N32</t>
+          <t>h_01KJCHDQPQD278545EC4FBQCEB</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-to-Microsoft-Dynamics-365-Finance-and-Operations-Integration/#h_01KG2C1TN9NB041EAF6T6Y1N32</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-to-Microsoft-Dynamics-365-Finance-and-Operations-Integration/#h_01KJCHDQPQD278545EC4FBQCEB</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Source Filter Settings</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01K04HD998SCMWKJ7BWM43V581</t>
+          <t>h_01KJCHEV7SG43WGKVBN4JB4HTA</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-to-Microsoft-Dynamics-365-Finance-and-Operations-Integration/#h_01K04HD998SCMWKJ7BWM43V581</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-to-Microsoft-Dynamics-365-Finance-and-Operations-Integration/#h_01KJCHEV7SG43WGKVBN4JB4HTA</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Role Assignments</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KG2CKG8AETJEVXMW5YZK4KS5</t>
+          <t>h_01KG29Y4CNTPQWG91Z1EST2X0G</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-to-Microsoft-Dynamics-365-Finance-and-Operations-Integration/#h_01KG2CKG8AETJEVXMW5YZK4KS5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-to-Microsoft-Dynamics-365-Finance-and-Operations-Integration/#h_01KG29Y4CNTPQWG91Z1EST2X0G</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Managing Table Data</t>
+          <t>Provisioning Settings</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KG2CK83YGVMDBK61KA3ZEJC8</t>
+          <t>h_01KG29Y4CNKA3PNXHKG6F1C70Q</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-to-Microsoft-Dynamics-365-Finance-and-Operations-Integration/#h_01KG2CK83YGVMDBK61KA3ZEJC8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-to-Microsoft-Dynamics-365-Finance-and-Operations-Integration/#h_01KG29Y4CNKA3PNXHKG6F1C70Q</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Provisioning Threshold</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01KJCHC57DDXAJWCEGW4Q6ZK6C</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-to-Microsoft-Dynamics-365-Finance-and-Operations-Integration/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-to-Microsoft-Dynamics-365-Finance-and-Operations-Integration/#h_01KJCHC57DDXAJWCEGW4Q6ZK6C</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Manage Warehouse Workers</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01KG2CNW0097M9V6P3HN9EBTNZ</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-to-Microsoft-Dynamics-365-Finance-and-Operations-Integration/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-to-Microsoft-Dynamics-365-Finance-and-Operations-Integration/#h_01KG2CNW0097M9V6P3HN9EBTNZ</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>Correlation Settings</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>h_01KJCHKWABYXARK7AVKQT9SN17</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-to-Microsoft-Dynamics-365-Finance-and-Operations-Integration/#h_01KJCHKWABYXARK7AVKQT9SN17</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Source Filter</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>h_01KJCJGB5KY5M566E789MYJTCF</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-to-Microsoft-Dynamics-365-Finance-and-Operations-Integration/#h_01KJCJGB5KY5M566E789MYJTCF</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Provisioning Settings</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>h_01KJCJ5V4GYAF6K50HSRV904C5</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-to-Microsoft-Dynamics-365-Finance-and-Operations-Integration/#h_01KJCJ5V4GYAF6K50HSRV904C5</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Provisioning Threshold</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>h_01KJCJN8ACE42A9R05FBQAFZSR</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-to-Microsoft-Dynamics-365-Finance-and-Operations-Integration/#h_01KJCJN8ACE42A9R05FBQAFZSR</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Manage Exflow Users</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>h_01KG2C841Q142BEN21DPBX6P3V</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-to-Microsoft-Dynamics-365-Finance-and-Operations-Integration/#h_01KG2C841Q142BEN21DPBX6P3V</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Correlation Settings</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>h_01KJCJVFFT5RVWSJQFNWF5TGHV</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-to-Microsoft-Dynamics-365-Finance-and-Operations-Integration/#h_01KJCJVFFT5RVWSJQFNWF5TGHV</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Source Filter Settings</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>h_01KJCQAEQ7WT9DCYVBJN95G40R</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-to-Microsoft-Dynamics-365-Finance-and-Operations-Integration/#h_01KJCQAEQ7WT9DCYVBJN95G40R</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Provisioning Settings</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>h_01KJCQAXD0AFG22TZT1CD4YKGF</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-to-Microsoft-Dynamics-365-Finance-and-Operations-Integration/#h_01KJCQAXD0AFG22TZT1CD4YKGF</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Notification Settings</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>h_01KG2B3A4GH06FW1RKHC69T6G9</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-to-Microsoft-Dynamics-365-Finance-and-Operations-Integration/#h_01KG2B3A4GH06FW1RKHC69T6G9</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Notification Report Settings</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>h_01KJCKFAR519KF5Y4Z9Z286HD6</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-to-Microsoft-Dynamics-365-Finance-and-Operations-Integration/#h_01KJCKFAR519KF5Y4Z9Z286HD6</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Notification Template for User Creation</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>h_01KJCKF0Z4EGP0MHZ56CHYTKTJ</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-to-Microsoft-Dynamics-365-Finance-and-Operations-Integration/#h_01KJCKF0Z4EGP0MHZ56CHYTKTJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Reporting Settings</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-to-Microsoft-Dynamics-365-Finance-and-Operations-Integration/#h_01K04B51EEX43EAV95YABBP3F5</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Log Insights Settings</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>h_01KJCMNB9JVPFFRSBP5ZPBYHQD</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-to-Microsoft-Dynamics-365-Finance-and-Operations-Integration/#h_01KJCMNB9JVPFFRSBP5ZPBYHQD</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Logging Settings</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>h_01KJCMZME785Y9JGRSHQ4QR0YS</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-to-Microsoft-Dynamics-365-Finance-and-Operations-Integration/#h_01KJCMZME785Y9JGRSHQ4QR0YS</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Developer Mode</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>h_01KJCN3ZBZQW44VG0QG2964XYQ</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-to-Microsoft-Dynamics-365-Finance-and-Operations-Integration/#h_01KJCN3ZBZQW44VG0QG2964XYQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Cache Handling</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>h_01KJCN3ZBZRBJSRHK7AH16Z2R9</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-to-Microsoft-Dynamics-365-Finance-and-Operations-Integration/#h_01KJCN3ZBZRBJSRHK7AH16Z2R9</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Attribute Map</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>h_01KJCNESDTGG464DS5HBT9KJZC</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-to-Microsoft-Dynamics-365-Finance-and-Operations-Integration/#h_01KJCNESDTGG464DS5HBT9KJZC</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Tables</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>h_01KJCNQZ6EPGQ3BMXZMQ1R3S56</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-to-Microsoft-Dynamics-365-Finance-and-Operations-Integration/#h_01KJCNQZ6EPGQ3BMXZMQ1R3S56</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Available Tables</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>h_01KJCNQZ6EFV8YTE35C3HN9ABV</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-to-Microsoft-Dynamics-365-Finance-and-Operations-Integration/#h_01KJCNQZ6EFV8YTE35C3HN9ABV</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Managing Table Data</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>h_01KJCNQZ6F9JNZ55Z5BC4AK9XN</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-to-Microsoft-Dynamics-365-Finance-and-Operations-Integration/#h_01KJCNQZ6F9JNZ55Z5BC4AK9XN</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-to-Microsoft-Dynamics-365-Finance-and-Operations-Integration/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-to-Microsoft-Dynamics-365-Finance-and-Operations-Integration/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-to-Microsoft-Dynamics-365-Finance-and-Operations-Integration/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
